--- a/human_validation/judge/kor/judge_D017_S001_P002__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D017_S001_P002__qwen3-235b_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -559,12 +556,82 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 걸 환영합니다. 오늘 저를 찾아오시게 된 일에 대해 말씀해 주시겠어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 제 얼굴에 대한 생각을 멈출 수가 없어서 왔어요. 왼쪽이 뭔가 비뚤어져 보여요, 뭔가 잘못된 것처럼요. 다른 사람들은 아무것도 안 보인다고 하는데, 창고에 있거나 살사의 밤에도 다들 그걸 알아채는 것 같은 느낌이 들어요. 그 생각을 머릿속에서 지우는 게 정말 힘들었어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 신체이형장애 (D017)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 얼굴에 대해 이렇게 느끼신 지 얼마나 되셨고, 그게 일하는 데나 살사의 밤 같은 활동을 즐기는 데 영향을 미쳤나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 정말 여러 가지를 망칠 만큼 오래됐어요. 직장에서는 자꾸 지체돼서 경고를 받았어요, 그냥 정상적으로 계속 움직이질 못하는 것처럼요. 그리고 네, 예전에 좋아하던 것들—축구, 살사의 밤, 심지어 가족 모임까지—을 빼먹기 시작했어요. 사람들이 절 쳐다보거나 사진 찍는 게 싫어서요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 신체이형장애 (D017); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 거울 확인하기, 얼굴 만지기, 다른 사람들과 비교하기처럼 얼굴을 고치거나 괜찮은지 확인하려고 반복적으로 하시는 행동이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 네. 많이 확인해요. 재고 현장에 다시 나가기 전에 화장실에 들러서 거울을 또 보고, 모자를 고쳐 쓰고, 얼굴의 같은 부위를 문지르면서 제대로 보이게 하려고 해요. 가끔은 의도했던 것보다 더 오래 그러다가 늦게 돌아가서 제 피킹 수치가 뒤처지고, 그러면 상사가 또 저한테 뭐라고 해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 신체이형장애 (D017) | 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>진단명: 신체이형장애 (D017)
 인구통계: 성별 남성 / 나이 30 / 직업상태 stocker or order filler / 최종학력 고등학교 졸업
@@ -573,131 +640,31 @@
 증상 지속 기간: None
 추가 요건: 
 주호소 증상 코드: S067
-배경 서술: 새로운 창고 관리자가 휴식 시간을 면밀히 감시하고 고객 현장 방문 때 직원들이 '단정해' 보이지 않는다고 공개적으로 비판하기 시작하면서 에두아르도의 어려움은 더 심해졌다. 출근 전의 자의식이 점차 얼굴에 결함이 있다고 느끼는 고정된 걱정으로 변했고, 그는 재고 현장으로 돌아가기 전에 외모를 확인하고 조정하고 머릿속으로 비교하는 데 점점 더 많은 시간을 쓰게 되었다. 이런 일과는 그의 물품 피킹 일정을 방해했고 반복적인 경고로 이어졌으며, 축구, 살사의 밤, 가족 모임에까지 번지기 시작해서 그는 늦게 나타나거나 사진 찍히는 걸 피했다. 직장에서 심각한 징계 면담이 있은 후, 그는 직원 지원 프로그램을 통한 의뢰를 받아들여 정신과 의사에게 평가를 받았다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 걸 환영합니다. 오늘 저를 찾아오시게 된 일에 대해 말씀해 주시겠어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 제 얼굴에 대한 생각을 멈출 수가 없어서 왔어요. 왼쪽이 뭔가 비뚤어져 보여요, 뭔가 잘못된 것처럼요. 다른 사람들은 아무것도 안 보인다고 하는데, 창고에 있거나 살사의 밤에도 다들 그걸 알아채는 것 같은 느낌이 들어요. 그 생각을 머릿속에서 지우는 게 정말 힘들었어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 신체이형장애 (D017)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 얼굴에 대해 이렇게 느끼신 지 얼마나 되셨고, 그게 일하는 데나 살사의 밤 같은 활동을 즐기는 데 영향을 미쳤나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 정말 여러 가지를 망칠 만큼 오래됐어요. 직장에서는 자꾸 지체돼서 경고를 받았어요, 그냥 정상적으로 계속 움직이질 못하는 것처럼요. 그리고 네, 예전에 좋아하던 것들—축구, 살사의 밤, 심지어 가족 모임까지—을 빼먹기 시작했어요. 사람들이 절 쳐다보거나 사진 찍는 게 싫어서요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 신체이형장애 (D017); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 거울 확인하기, 얼굴 만지기, 다른 사람들과 비교하기처럼 얼굴을 고치거나 괜찮은지 확인하려고 반복적으로 하시는 행동이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 네. 많이 확인해요. 재고 현장에 다시 나가기 전에 화장실에 들러서 거울을 또 보고, 모자를 고쳐 쓰고, 얼굴의 같은 부위를 문지르면서 제대로 보이게 하려고 해요. 가끔은 의도했던 것보다 더 오래 그러다가 늦게 돌아가서 제 피킹 수치가 뒤처지고, 그러면 상사가 또 저한테 뭐라고 해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
+배경 서술: 새로운 창고 관리자가 휴식 시간을 면밀히 감시하고 고객 현장 방문 때 직원들이 '단정해' 보이지 않는다고 공개적으로 비판하기 시작하면서 에두아르도의 어려움은 더 심해졌다. 출근 전의 자의식이 점차 얼굴에 결함이 있다고 느끼는 고정된 걱정으로 변했고, 그는 재고 현장으로 돌아가기 전에 외모를 확인하고 조정하고 머릿속으로 비교하는 데 점점 더 많은 시간을 쓰게 되었다. 이런 일과는 그의 물품 피킹 일정을 방해했고 반복적인 경고로 이어졌으며, 축구, 살사의 밤, 가족 모임에까지 번지기 시작해서 그는 늦게 나타나거나 사진 찍히는 걸 피했다. 직장에서 심각한 징계 면담이 있은 후, 그는 직원 지원 프로그램을 통한 의뢰를 받아들여 정신과 의사에게 평가를 받았다.
+표집된 증상 목록:
+  - S067 외모 집착: 타인에게는 관찰되지 않거나 경미하게 보이는 신체적 결함이나 흠에 대한 한 가지 이상의 집착.
+  - S068 외모 관련 반복 행동: 외모에 대한 걱정에 반응하여 수행하는 반복적 행동이나 정신적 활동.</t>
+        </is>
+      </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>[3번째 턴 · 의사의 감별진단] 고확률: 신체이형장애 (D017) | 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 신체이형장애 (D017, ICD: F45.22)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: dysmorphic_symptoms (관계=must_include, 요구개수=2, 충족개수=2, 커버리지=1.0)
-  확인된 근거: 외모 집착: 타인에게는 관찰되지 않거나 경미하게 보이는 신체적 결함이나 흠에 대한 한 가지 이상의 집착.; 외모 관련 반복 행동: 외모에 대한 걱정에 반응하여 수행하는 반복적 행동이나 정신적 활동.
-  누락: (없음)</t>
+          <t>의사의 최종 진단: 신체이형장애 (D017, ICD: F45.22)
+지속 기간 요건: None
+기능적 손상 요건: 있음
+추가 요건: None
+체크리스트 그룹: dysmorphic_symptoms (관계=must_include, 요구개수=2, 충족개수=2, 커버리지=1.0)
+확인된 근거:
+  - 외모 집착: 타인에게는 관찰되지 않거나 경미하게 보이는 신체적 결함이나 흠에 대한 한 가지 이상의 집착.
+  - 외모 관련 반복 행동: 외모에 대한 걱정에 반응하여 수행하는 반복적 행동이나 정신적 활동.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A25:B25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D017_S001_P002__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D017_S001_P002__qwen3-235b_kor.xlsx
@@ -626,6 +626,11 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -660,11 +665,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A25:B25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D017_S001_P002__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D017_S001_P002__qwen3-235b_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.037</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="5">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.037</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="7">
@@ -553,6 +554,7 @@
         <v>1</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
